--- a/eagle_eye/out/demo/QC_Checklist_FILLED_v2.xlsx
+++ b/eagle_eye/out/demo/QC_Checklist_FILLED_v2.xlsx
@@ -1,15 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QC Checklist" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="QC Checklist" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'QC Checklist'!$A$1:$H$42</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,8 +35,22 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000F2742"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00374151"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -55,8 +72,18 @@
         <fgColor rgb="000F2742"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E11D48"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -64,15 +91,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00D1D5DB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,7 +483,139 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>EAGLE EYE · Cabinet QC</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Cabinet</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>EE-DEMO-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>photo_v2.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Inspected</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-10-16T19:57:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>SKIP (root cause elsewhere)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Items checked</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -448,1563 +625,1627 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Item ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>Expected</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>Found</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Re-check</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>GA-PS11</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>PS11 present (psu)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>Installed</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>Present</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>slot occupancy 92%; label seen: True</t>
         </is>
       </c>
+      <c r="H2" s="8" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>GA-PS12</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>PS12 present (psu)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>Installed</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>Present</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>Marker #1 | slot occupancy 92%; label seen: True</t>
         </is>
       </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>GA-D12</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>D12 present (controller)</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Installed</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Present</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>slot occupancy 100%; label seen: True</t>
         </is>
       </c>
+      <c r="H4" s="8" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>GA-CB41</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>CB41 present (breaker)</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Installed</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>Present</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>slot occupancy 99%; label seen: True</t>
         </is>
       </c>
+      <c r="H5" s="8" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>GA-CB42</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>CB42 present (breaker)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>Installed</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>Present</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>slot occupancy 99%; label seen: True</t>
         </is>
       </c>
+      <c r="H6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>GA-CB43</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>CB43 present (breaker)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>Installed</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>Present</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>slot occupancy 99%; label seen: True</t>
         </is>
       </c>
+      <c r="H7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>GA-CB44</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>CB44 present (breaker)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>Installed</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>Present</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>slot occupancy 98%; label seen: True</t>
         </is>
       </c>
+      <c r="H8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>GA-1CBP01</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>1CBP01 present (baseplate)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>Installed</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>Present</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>slot occupancy 100%; label seen: True</t>
         </is>
       </c>
+      <c r="H9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>GA-1CBP02</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>1CBP02 present (baseplate)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>Installed</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>Present</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>slot occupancy 100%; label seen: True</t>
         </is>
       </c>
+      <c r="H10" s="8" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>GA-1CBP03</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>1CBP03 present (baseplate)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>Installed</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>Present</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>slot occupancy 100%; label seen: True</t>
         </is>
       </c>
+      <c r="H11" s="8" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>GA-1CBP04</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>1CBP04 present (baseplate)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>Installed</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>Present</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>slot occupancy 100%; label seen: True</t>
         </is>
       </c>
+      <c r="H12" s="8" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>GA-PE</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>PE present (earth)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>Installed</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>Present</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>slot occupancy 100%; label seen: True</t>
         </is>
       </c>
+      <c r="H13" s="8" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>ORD-RAIL-1</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>ORDER</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>Breaker order on RAIL-1</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>CB41-CB42-CB43-CB44</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>CB41-CB42-CB43-CB44</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>Marker #2 | read along rail: CB41-CB42-CB43-CB44</t>
         </is>
       </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>LBL-PS11</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>LABEL</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>PS11 device label</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>PS11</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>PS11</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>label sticker+print found: True; OCR votes ['PS11', 'PS11', 'PS11', 'PS11']</t>
         </is>
       </c>
+      <c r="H15" s="8" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>LBL-PS12</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>LABEL</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>PS12 device label</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>PS12</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>PS12</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>label sticker+print found: True; OCR votes ['PS12', 'PS12', 'PS12', 'PS12']</t>
         </is>
       </c>
+      <c r="H16" s="8" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>LBL-D12</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>LABEL</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>D12 device label</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>D12</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>D12</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>label sticker+print found: True; OCR votes ['D12', 'D12', 'D12', 'D12']</t>
         </is>
       </c>
+      <c r="H17" s="8" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>LBL-CB41</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>LABEL</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>CB41 device label</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>CB41</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>CB41</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>read on rail</t>
         </is>
       </c>
+      <c r="H18" s="8" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>LBL-CB42</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>LABEL</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>CB42 device label</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>CB42</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>CB42</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>read on rail</t>
         </is>
       </c>
+      <c r="H19" s="8" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>LBL-CB43</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>LABEL</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>CB43 device label</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>CB43</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>CB43</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>read on rail</t>
         </is>
       </c>
+      <c r="H20" s="8" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>LBL-CB44</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>LABEL</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>CB44 device label</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>CB44</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>CB44</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>read on rail</t>
         </is>
       </c>
+      <c r="H21" s="8" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>LBL-1CBP01</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>LABEL</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>1CBP01 device label</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>1CBP01</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>1CBP01</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>label sticker+print found: True; OCR votes ['1CBPO1', '1CBPO1', '1CBPO1', '1CBPO1']</t>
         </is>
       </c>
+      <c r="H22" s="8" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>LBL-1CBP02</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>LABEL</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>1CBP02 device label</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>1CBP02</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>1CBP02</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>label sticker+print found: True; OCR votes ['1CBPO02', '1CBPO02', '1CBPO2', '1CBPO2']</t>
         </is>
       </c>
+      <c r="H23" s="8" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>LBL-1CBP03</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>LABEL</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>1CBP03 device label</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>1CBP03</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>1CBP03</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>Marker #3 | label sticker+print found: True; OCR votes ['1CBP03', '1CBP03', '1CBPO3', '1CBP03']</t>
         </is>
       </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>LBL-1CBP04</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>LABEL</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>1CBP04 device label</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>1CBP04</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>1CBP04</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>label sticker+print found: True; OCR votes ['1CBP04', '1CBP04', '1CBP04', '1CBP04']</t>
         </is>
       </c>
+      <c r="H25" s="8" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>LBL-PE</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>LABEL</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>PE device label</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>PE</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>PE</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>label sticker+print found: True; OCR votes ['PE', 'PE', 'PE', 'PE']</t>
         </is>
       </c>
+      <c r="H26" s="8" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>FER-X3:1</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>FERRULE</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>Ferrule on X3:1 wire</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>X3-1/CB41-2</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>X3-1/CB41-2</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
         <is>
           <t>OCR votes ['X3-1/CB41-2', 'X3-1/CB41-2', 'X3-1/CB41-2', 'X3-1/CB41-2']</t>
         </is>
       </c>
+      <c r="H27" s="8" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>FER-X3:2</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>FERRULE</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>Ferrule on X3:2 wire</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>X3-2/CB42-2</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>X3-2/CB42-2</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>OCR votes ['X3-2/CB42-2', 'X3-2/CB42-2', 'X3-2/CB42-2', 'X3-2/CB42-2']</t>
         </is>
       </c>
+      <c r="H28" s="8" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>FER-X3:3</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>FERRULE</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>Ferrule on X3:3 wire</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>X3-3/CB43-2</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>No ferrule</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F29" s="10" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>Marker #4 | sleeve pixels 0%</t>
         </is>
       </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>FER-X3:4</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>FERRULE</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>Ferrule on X3:4 wire</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>X3-4/CB44-2</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>X3-4/CB44-2</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
         <is>
           <t>OCR votes ['X3-4/CB44-2', 'X3-4/CB44-2', 'X3-4/CB44-2', 'X3-4/CB44-2']</t>
         </is>
       </c>
+      <c r="H30" s="8" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>FER-X3:5</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>FERRULE</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>Ferrule on X3:5 wire</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>X3-5/PS11+</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>X3-5/PS11+</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>OCR votes ['X3-5/PS11+', 'X3-5/PS11+', 'X3-5/PS11+', 'X3-5/PS11+']</t>
         </is>
       </c>
+      <c r="H31" s="8" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>FER-X3:6</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>FERRULE</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>Ferrule on X3:6 wire</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t>X3-6/PS11-</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t>X3-6/PS11-</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
         <is>
           <t>OCR votes ['X3-6/PS11-', 'X3-6/PS11-', 'X3-6/PS11-', 'X3-6/PS11-']</t>
         </is>
       </c>
+      <c r="H32" s="8" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>FER-X3:7</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>FERRULE</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>Ferrule on X3:7 wire</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>X3-7/D12-L</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t>X3-7/D12-L</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t>OCR votes ['X3-7/D12-L', 'X3-7/D12-L', 'X3-7/D12-L', 'X3-7/D12-L']</t>
         </is>
       </c>
+      <c r="H33" s="8" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>FER-X3:8</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>FERRULE</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>Ferrule on X3:8 wire</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>X3-8/PE-1</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>X3-8/PE-1</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t>OCR votes ['X3-8/PE-1', 'X3-8/PE-1', 'X3-8/PE-1', 'X3-8/PE-1']</t>
         </is>
       </c>
+      <c r="H34" s="8" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>COL-X3:1</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>COLOUR</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>Wire colour at X3:1</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>BN</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>BN</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
         <is>
           <t>green 0% yellow 0%</t>
         </is>
       </c>
+      <c r="H35" s="8" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>COL-X3:2</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>COLOUR</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>Wire colour at X3:2</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>BN</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>BN</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
         <is>
           <t>green 0% yellow 0%</t>
         </is>
       </c>
+      <c r="H36" s="8" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>COL-X3:3</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>COLOUR</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>Wire colour at X3:3</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="8" t="inlineStr">
         <is>
           <t>BN</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>BN</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
         <is>
           <t>green 0% yellow 0%</t>
         </is>
       </c>
+      <c r="H37" s="8" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>COL-X3:4</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>COLOUR</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>Wire colour at X3:4</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="8" t="inlineStr">
         <is>
           <t>BN</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="8" t="inlineStr">
         <is>
           <t>BN</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
         <is>
           <t>green 0% yellow 0%</t>
         </is>
       </c>
+      <c r="H38" s="8" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>COL-X3:5</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>COLOUR</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>Wire colour at X3:5</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>RD</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>RD</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
         <is>
           <t>green 0% yellow 0%</t>
         </is>
       </c>
+      <c r="H39" s="8" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>COL-X3:6</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>COLOUR</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>Wire colour at X3:6</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="8" t="inlineStr">
         <is>
           <t>BK</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="8" t="inlineStr">
         <is>
           <t>BK</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
         <is>
           <t>green 0% yellow 0%</t>
         </is>
       </c>
+      <c r="H40" s="8" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>COL-X3:7</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>COLOUR</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>Wire colour at X3:7</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t>BU</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>BU</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
         <is>
           <t>green 0% yellow 0%</t>
         </is>
       </c>
+      <c r="H41" s="8" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>COL-X3:8</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>COLOUR</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>Wire colour at X3:8</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="8" t="inlineStr">
         <is>
           <t>GNYE</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="8" t="inlineStr">
         <is>
           <t>GNYE</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
         <is>
           <t>green 53% yellow 40%</t>
         </is>
       </c>
+      <c r="H42" s="8" t="n"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>